--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CDP.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.5</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>12.0</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,11 @@
           <t>diff_casa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (18)</t>
+          <t>Q2 (12)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q1 (-9)</t>
+          <t>Q1 (-4)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,12 +701,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (18)</t>
+          <t>Diff médio casa: 4 | fora: 20</t>
         </is>
       </c>
     </row>
@@ -714,12 +718,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pior período: Q1 (-9)</t>
+          <t>Melhor período: Q2 (12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pior período: Q1 (-4)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -824,8 +840,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3" t="n">
+        <v>69</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>73</v>
+      </c>
+      <c r="H3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,233 +973,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
       <c r="E2" t="n">
-        <v>27.1</v>
+        <v>22.6</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>12</v>
+      </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>D. Buccilli</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
       <c r="E3" t="n">
-        <v>22.4</v>
+        <v>20.2</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
       <c r="E4" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="F4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I4" t="n">
         <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" t="n">
-        <v>25</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Costa</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-3</v>
+      </c>
       <c r="E5" t="n">
-        <v>17.7</v>
+        <v>19.8</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
       <c r="E6" t="n">
-        <v>20.2</v>
+        <v>24.9</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>-3</v>
+      </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>J. Pedro</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
       <c r="E7" t="n">
-        <v>17.2</v>
+        <v>10.1</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>-5</v>
+      </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" t="n">
-        <v>22.6</v>
+        <v>17.7</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-7</v>
+      </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
       <c r="E9" t="n">
-        <v>19.8</v>
+        <v>27.1</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>-9</v>
+      </c>
       <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1260,25 +1373,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -1303,25 +1416,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I3" t="n">
-        <v>25</v>
+        <v>21.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1346,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
         <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="n">
         <v>12</v>
       </c>
-      <c r="H5" t="n">
-        <v>14</v>
-      </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>20.5</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1534,84 +1647,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -1620,124 +1733,124 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -1745,101 +1858,117 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1848,40 +1977,56 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1892,7 +2037,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1905,14 +2050,14 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1922,13 +2067,13 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1943,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2021,8 +2166,37 @@
         <v>20</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922724</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F3" t="n">
+        <v>69</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CDP.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>75.3</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>70.3</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (12)</t>
+          <t>Q2 (7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q1 (-4)</t>
+          <t>Q1 (-4.3)</t>
         </is>
       </c>
     </row>
@@ -679,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,19 +706,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 4 | fora: 20</t>
+          <t>Diff médio casa: 4 | fora: 5.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (12)</t>
+          <t>Diff médio em vitórias: 12 | em derrotas: -9</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q1 (-4)</t>
+          <t>Melhor período: Q2 (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q1 (-4.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D. Buccilli sobe mais em vitórias (7.5 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -746,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -815,35 +839,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>-9</v>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H2" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -855,26 +879,59 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H3" t="n">
+        <v>64</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>73</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>69</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>73</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>69</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -973,261 +1030,303 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.5</v>
+        <v>16.9</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>22.6</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>-5.5</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-18</v>
+      </c>
       <c r="L2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.9</v>
+        <v>14.7</v>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
         <v>10</v>
       </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
-      </c>
       <c r="H3" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>12</v>
+      </c>
       <c r="L3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.9</v>
+        <v>9.5</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="E4" t="n">
-        <v>22.4</v>
+        <v>16.6</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-6</v>
+      </c>
       <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
         <v>-3</v>
       </c>
-      <c r="E5" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="n">
-        <v>24.9</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
       <c r="L6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.3</v>
+        <v>23.4</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1</v>
+      </c>
       <c r="L7" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.1</v>
+        <v>28.5</v>
       </c>
       <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>-7</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1373,25 +1472,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="I2" t="n">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="J2" t="n">
-        <v>22.5</v>
+        <v>20.7</v>
       </c>
       <c r="K2" t="n">
-        <v>-4</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="3">
@@ -1416,25 +1515,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>21.5</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1459,22 +1558,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H4" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>19.7</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>21.7</v>
       </c>
       <c r="K4" t="n">
         <v>-2</v>
@@ -1502,25 +1601,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>20.5</v>
+        <v>19.3</v>
       </c>
       <c r="J5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
@@ -1539,19 +1638,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
@@ -1651,28 +1750,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1684,16 +1783,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1702,99 +1801,99 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0.5</v>
@@ -1803,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1816,40 +1915,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="C5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.5</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1858,175 +1957,175 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5</v>
-      </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="C8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2088,7 +2187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2195,8 +2294,37 @@
         <v>4</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922729</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F4" t="n">
+        <v>78</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CDP.xlsx
@@ -18,11 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.2</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>72.8</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-2.5</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (7)</t>
+          <t>Q4 (4)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q1 (-4.3)</t>
+          <t>Q1 (-2.8)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 4 | fora: 5.5</t>
+          <t>Diff médio casa: -2.5 | fora: 5.5</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (7)</t>
+          <t>Melhor período: Q4 (4)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q1 (-4.3)</t>
+          <t>Pior período: Q1 (-2.8)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Buccilli sobe mais em vitórias (7.5 ppg).</t>
+          <t>D. Buccilli sobe mais em vitórias (4.5 ppg).</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -905,33 +905,66 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>71</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>71</v>
+      </c>
+      <c r="H4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>73</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>69</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>73</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>69</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -945,7 +978,7 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1037,10 +1070,10 @@
         <v>16.9</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>-3.5</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
@@ -1058,139 +1091,139 @@
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.7</v>
+        <v>24.9</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>-6</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>17.1</v>
+        <v>23.2</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="L3" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.5</v>
+        <v>16.3</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
         <v>-3</v>
       </c>
-      <c r="E4" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.9</v>
+        <v>9.5</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>-0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>23.2</v>
+        <v>16.6</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5</v>
+        <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
@@ -1206,13 +1239,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.1</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D6" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
         <v>22</v>
@@ -1230,140 +1263,146 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.4</v>
+        <v>20.6</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>-5.5</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>27.1</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="L7" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.5</v>
+        <v>25.9</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="n">
-        <v>26</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>12</v>
       </c>
-      <c r="G8" t="n">
-        <v>7.5</v>
-      </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" t="n">
         <v>12.5</v>
       </c>
-      <c r="J8" t="n">
-        <v>22</v>
-      </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.2</v>
+        <v>28.9</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="L9" t="n">
-        <v>-9</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-11</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1472,25 +1511,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H2" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="I2" t="n">
-        <v>16.3</v>
+        <v>17.8</v>
       </c>
       <c r="J2" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.3</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="3">
@@ -1515,25 +1554,25 @@
         </is>
       </c>
       <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>74</v>
+      </c>
+      <c r="G3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" t="n">
-        <v>39</v>
-      </c>
-      <c r="H3" t="n">
-        <v>21</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1558,25 +1597,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="I4" t="n">
-        <v>19.7</v>
+        <v>18.2</v>
       </c>
       <c r="J4" t="n">
-        <v>21.7</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>-2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="5">
@@ -1601,25 +1640,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1637,20 +1676,20 @@
   <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
@@ -1746,87 +1785,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.333333333333333</v>
+        <v>5.8</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="F2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.7</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>1.333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1835,59 +1874,59 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1896,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1905,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -1915,52 +1954,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.333333333333333</v>
+        <v>2.8</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.666666666666667</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -1970,19 +2009,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1991,13 +2030,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2006,10 +2045,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -2025,52 +2064,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -2080,28 +2119,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.7</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>1.333333333333333</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2110,22 +2149,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.3</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.5</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.3</v>
-      </c>
       <c r="P8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9">
@@ -2134,29 +2173,35 @@
           <t>J. Rodrigues</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2164,15 +2209,17 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2187,11 +2234,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2323,8 +2370,37 @@
         <v>-9</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2922735</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>